--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="145">
   <si>
     <t/>
   </si>
@@ -289,6 +289,15 @@
     <t>33</t>
   </si>
   <si>
+    <t>20144200</t>
+  </si>
+  <si>
+    <t>WALLS MGM BLBRY CHEE</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
     <t>20032368</t>
   </si>
   <si>
@@ -337,12 +346,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>20136391</t>
-  </si>
-  <si>
-    <t>WALLS POPLRE MANGO90</t>
-  </si>
-  <si>
     <t>20140731</t>
   </si>
   <si>
@@ -398,12 +401,6 @@
   </si>
   <si>
     <t>CRNTTO RS CHO CHS134</t>
-  </si>
-  <si>
-    <t>20133149</t>
-  </si>
-  <si>
-    <t>PAD.POP UPIN&amp;IPIN 60</t>
   </si>
   <si>
     <t>20136703</t>
@@ -841,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1463,21 +1460,21 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1486,7 +1483,7 @@
         <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1494,10 +1491,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1506,18 +1503,18 @@
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1526,7 +1523,7 @@
         <v>8</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>19</v>
@@ -1534,10 +1531,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1546,10 +1543,10 @@
         <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1566,18 +1563,18 @@
         <v>8</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1586,7 +1583,7 @@
         <v>8</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>19</v>
@@ -1606,7 +1603,7 @@
         <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>19</v>
@@ -1614,10 +1611,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -1634,10 +1631,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1654,10 +1651,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1674,10 +1671,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1686,7 +1683,7 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -1694,10 +1691,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1714,10 +1711,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1734,10 +1731,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -1754,10 +1751,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -1774,10 +1771,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -1794,10 +1791,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -1806,7 +1803,7 @@
         <v>8</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>19</v>
@@ -1814,10 +1811,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -1826,18 +1823,18 @@
         <v>8</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -1846,18 +1843,18 @@
         <v>8</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -1866,7 +1863,7 @@
         <v>8</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>19</v>
@@ -1874,10 +1871,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -1886,7 +1883,7 @@
         <v>8</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>19</v>
@@ -1894,10 +1891,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -1906,18 +1903,18 @@
         <v>8</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -1926,29 +1923,9 @@
         <v>8</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F55" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/RWS05N.xlsx
+++ b/RWS05N.xlsx
@@ -175,7 +175,7 @@
     <t>20134926</t>
   </si>
   <si>
-    <t>WALL ICE CRM OREO 80</t>
+    <t>WALLS ICE OREO 80 ML</t>
   </si>
   <si>
     <t>21</t>
@@ -256,7 +256,7 @@
     <t>20129821</t>
   </si>
   <si>
-    <t>MAGNUM MATCHA.CRBL80</t>
+    <t>WALLS MAG MT.C 80 ML</t>
   </si>
   <si>
     <t>30</t>
@@ -301,25 +301,25 @@
     <t>20032368</t>
   </si>
   <si>
-    <t>WALL'S MAGNUM ALMD80</t>
+    <t>WALLS MAG ALMD 80 ML</t>
   </si>
   <si>
     <t>20032366</t>
   </si>
   <si>
-    <t>WALL'S MAGNUM CLAS80</t>
+    <t>WALLS MAG CLAS 80 ML</t>
   </si>
   <si>
     <t>20134689</t>
   </si>
   <si>
-    <t>MAGNUM MNGO YOGHRT80</t>
+    <t>WALLS MAG M.YO 80 ML</t>
   </si>
   <si>
     <t>20138475</t>
   </si>
   <si>
-    <t>WALLS MGNUM STRW PAN</t>
+    <t>WALLS MAG ST.P 80 ML</t>
   </si>
   <si>
     <t>20054385</t>
